--- a/saidas/comparativo_preselecionados_valor.xlsx
+++ b/saidas/comparativo_preselecionados_valor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Modelo</t>
   </si>
@@ -52,46 +52,73 @@
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
+    <t>ExtraTrees(EXT,j90)</t>
+  </si>
+  <si>
+    <t>POLY+ABR</t>
+  </si>
+  <si>
+    <t>SE(ETR)+SE(RFR)+LSVR</t>
+  </si>
+  <si>
+    <t>MAS+OHE+MAS+OHE+SE(SGDR)+MMS+LSVR</t>
+  </si>
+  <si>
+    <t>VotingRegressor (RandomForest + ExtraTrees + XGBoost)</t>
+  </si>
+  <si>
     <t>SE(ETR)+ABR</t>
   </si>
   <si>
-    <t>ExtraTrees(EXT,j90)</t>
-  </si>
-  <si>
-    <t>Voting(GBR+XGB+RFR)</t>
-  </si>
-  <si>
     <t>97/211</t>
   </si>
   <si>
-    <t>83/209</t>
-  </si>
-  <si>
-    <t>97/209</t>
-  </si>
-  <si>
-    <t>81/209</t>
+    <t>92/209</t>
+  </si>
+  <si>
+    <t>75/209</t>
+  </si>
+  <si>
+    <t>84/209</t>
+  </si>
+  <si>
+    <t>76/209</t>
+  </si>
+  <si>
+    <t>90/209</t>
+  </si>
+  <si>
+    <t>79/209</t>
   </si>
   <si>
     <t>156/211</t>
   </si>
   <si>
+    <t>164/209</t>
+  </si>
+  <si>
+    <t>144/209</t>
+  </si>
+  <si>
     <t>136/209</t>
   </si>
   <si>
-    <t>159/209</t>
-  </si>
-  <si>
-    <t>144/209</t>
+    <t>132/209</t>
+  </si>
+  <si>
+    <t>147/209</t>
+  </si>
+  <si>
+    <t>143/209</t>
   </si>
   <si>
     <t>211/211</t>
   </si>
   <si>
+    <t>209/209</t>
+  </si>
+  <si>
     <t>208/209</t>
-  </si>
-  <si>
-    <t>209/209</t>
   </si>
 </sst>
 </file>
@@ -449,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -513,13 +540,13 @@
         <v>39.52</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -527,34 +554,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>8.69</v>
+        <v>7.2</v>
       </c>
       <c r="D3">
-        <v>11.73</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="F3">
-        <v>10237</v>
+        <v>79400.8</v>
       </c>
       <c r="G3">
-        <v>546768.7</v>
+        <v>450801</v>
       </c>
       <c r="H3">
-        <v>73.83</v>
+        <v>42.56</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -562,34 +589,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>7.21</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="D4">
-        <v>9.58</v>
+        <v>10.33</v>
       </c>
       <c r="E4">
-        <v>0.73</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F4">
-        <v>7292</v>
+        <v>113974.9</v>
       </c>
       <c r="G4">
-        <v>449005.7</v>
+        <v>472644.7</v>
       </c>
       <c r="H4">
-        <v>41.44</v>
+        <v>32.44</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -597,34 +624,139 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>8.289999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D5">
-        <v>10.81</v>
+        <v>10.56</v>
       </c>
       <c r="E5">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="F5">
-        <v>7921.2</v>
+        <v>134800.5</v>
       </c>
       <c r="G5">
-        <v>495643.8</v>
+        <v>486255.9</v>
       </c>
       <c r="H5">
-        <v>37.54</v>
+        <v>36.01</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="D6">
+        <v>10.57</v>
+      </c>
+      <c r="E6">
+        <v>0.651</v>
+      </c>
+      <c r="F6">
+        <v>90614.89999999999</v>
+      </c>
+      <c r="G6">
+        <v>502619.6</v>
+      </c>
+      <c r="H6">
+        <v>30.92</v>
+      </c>
+      <c r="I6" t="s">
         <v>22</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
+      <c r="J6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>8.01</v>
+      </c>
+      <c r="D7">
+        <v>10.58</v>
+      </c>
+      <c r="E7">
+        <v>0.664</v>
+      </c>
+      <c r="F7">
+        <v>142117.2</v>
+      </c>
+      <c r="G7">
+        <v>480761.3</v>
+      </c>
+      <c r="H7">
+        <v>35.51</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>26</v>
+      </c>
+      <c r="C8">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="D8">
+        <v>11.72</v>
+      </c>
+      <c r="E8">
+        <v>0.582</v>
+      </c>
+      <c r="F8">
+        <v>130733.2</v>
+      </c>
+      <c r="G8">
+        <v>543600</v>
+      </c>
+      <c r="H8">
+        <v>77.39</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/saidas/comparativo_preselecionados_valor.xlsx
+++ b/saidas/comparativo_preselecionados_valor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>Modelo</t>
   </si>
@@ -52,6 +52,9 @@
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
+    <t>SARIMAX</t>
+  </si>
+  <si>
     <t>ExtraTrees(EXT,j90)</t>
   </si>
   <si>
@@ -64,15 +67,18 @@
     <t>MAS+OHE+MAS+OHE+SE(SGDR)+MMS+LSVR</t>
   </si>
   <si>
-    <t>VotingRegressor (RandomForest + ExtraTrees + XGBoost)</t>
-  </si>
-  <si>
     <t>SE(ETR)+ABR</t>
   </si>
   <si>
+    <t>Voting(GBR+XGB+RFR)</t>
+  </si>
+  <si>
     <t>97/211</t>
   </si>
   <si>
+    <t>91/209</t>
+  </si>
+  <si>
     <t>92/209</t>
   </si>
   <si>
@@ -85,15 +91,18 @@
     <t>76/209</t>
   </si>
   <si>
-    <t>90/209</t>
-  </si>
-  <si>
     <t>79/209</t>
   </si>
   <si>
+    <t>85/209</t>
+  </si>
+  <si>
     <t>156/211</t>
   </si>
   <si>
+    <t>153/209</t>
+  </si>
+  <si>
     <t>164/209</t>
   </si>
   <si>
@@ -106,10 +115,10 @@
     <t>132/209</t>
   </si>
   <si>
-    <t>147/209</t>
-  </si>
-  <si>
     <t>143/209</t>
+  </si>
+  <si>
+    <t>146/209</t>
   </si>
   <si>
     <t>211/211</t>
@@ -476,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -519,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>7.19</v>
@@ -540,13 +549,13 @@
         <v>39.52</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -554,34 +563,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>7.2</v>
+        <v>7.09</v>
       </c>
       <c r="D3">
-        <v>9.609999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="E3">
-        <v>0.72</v>
+        <v>0.756</v>
       </c>
       <c r="F3">
-        <v>79400.8</v>
+        <v>8302.9</v>
       </c>
       <c r="G3">
-        <v>450801</v>
+        <v>426761.2</v>
       </c>
       <c r="H3">
-        <v>42.56</v>
+        <v>31.57</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -592,31 +601,31 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>8.119999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="D4">
-        <v>10.33</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E4">
-        <v>0.6840000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="F4">
-        <v>113974.9</v>
+        <v>79400.8</v>
       </c>
       <c r="G4">
-        <v>472644.7</v>
+        <v>450801</v>
       </c>
       <c r="H4">
-        <v>32.44</v>
+        <v>42.56</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -627,31 +636,31 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>8.109999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="D5">
-        <v>10.56</v>
+        <v>10.33</v>
       </c>
       <c r="E5">
-        <v>0.659</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F5">
-        <v>134800.5</v>
+        <v>113974.9</v>
       </c>
       <c r="G5">
-        <v>486255.9</v>
+        <v>472644.7</v>
       </c>
       <c r="H5">
-        <v>36.01</v>
+        <v>32.44</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -662,31 +671,31 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>8.449999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="D6">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
       <c r="E6">
-        <v>0.651</v>
+        <v>0.659</v>
       </c>
       <c r="F6">
-        <v>90614.89999999999</v>
+        <v>134800.5</v>
       </c>
       <c r="G6">
-        <v>502619.6</v>
+        <v>486255.9</v>
       </c>
       <c r="H6">
-        <v>30.92</v>
+        <v>36.01</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -697,31 +706,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>8.01</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D7">
-        <v>10.58</v>
+        <v>10.57</v>
       </c>
       <c r="E7">
-        <v>0.664</v>
+        <v>0.651</v>
       </c>
       <c r="F7">
-        <v>142117.2</v>
+        <v>90614.89999999999</v>
       </c>
       <c r="G7">
-        <v>480761.3</v>
+        <v>502619.6</v>
       </c>
       <c r="H7">
-        <v>35.51</v>
+        <v>30.92</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -729,7 +738,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>8.529999999999999</v>
@@ -750,13 +759,48 @@
         <v>77.39</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>7.97</v>
+      </c>
+      <c r="D9">
+        <v>10.65</v>
+      </c>
+      <c r="E9">
+        <v>0.66</v>
+      </c>
+      <c r="F9">
+        <v>134676.1</v>
+      </c>
+      <c r="G9">
+        <v>485427.5</v>
+      </c>
+      <c r="H9">
+        <v>33.35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
         <v>34</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/saidas/comparativo_preselecionados_valor.xlsx
+++ b/saidas/comparativo_preselecionados_valor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>Modelo</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
-    <t>SARIMAX</t>
+    <t>SARIMA</t>
   </si>
   <si>
     <t>ExtraTrees(EXT,j90)</t>
@@ -61,73 +61,67 @@
     <t>POLY+ABR</t>
   </si>
   <si>
-    <t>SE(ETR)+SE(RFR)+LSVR</t>
-  </si>
-  <si>
     <t>MAS+OHE+MAS+OHE+SE(SGDR)+MMS+LSVR</t>
   </si>
   <si>
+    <t>VotingRegressor (RandomForest + ExtraTrees + XGBoost)</t>
+  </si>
+  <si>
     <t>SE(ETR)+ABR</t>
   </si>
   <si>
     <t>Voting(GBR+XGB+RFR)</t>
   </si>
   <si>
-    <t>97/211</t>
-  </si>
-  <si>
-    <t>91/209</t>
-  </si>
-  <si>
-    <t>92/209</t>
-  </si>
-  <si>
-    <t>75/209</t>
-  </si>
-  <si>
-    <t>84/209</t>
-  </si>
-  <si>
-    <t>76/209</t>
-  </si>
-  <si>
-    <t>79/209</t>
-  </si>
-  <si>
-    <t>85/209</t>
-  </si>
-  <si>
-    <t>156/211</t>
-  </si>
-  <si>
-    <t>153/209</t>
-  </si>
-  <si>
-    <t>164/209</t>
-  </si>
-  <si>
-    <t>144/209</t>
-  </si>
-  <si>
-    <t>136/209</t>
-  </si>
-  <si>
-    <t>132/209</t>
-  </si>
-  <si>
-    <t>143/209</t>
-  </si>
-  <si>
-    <t>146/209</t>
-  </si>
-  <si>
-    <t>211/211</t>
-  </si>
-  <si>
-    <t>209/209</t>
-  </si>
-  <si>
-    <t>208/209</t>
+    <t>72/203</t>
+  </si>
+  <si>
+    <t>86/202</t>
+  </si>
+  <si>
+    <t>89/202</t>
+  </si>
+  <si>
+    <t>72/202</t>
+  </si>
+  <si>
+    <t>69/202</t>
+  </si>
+  <si>
+    <t>73/202</t>
+  </si>
+  <si>
+    <t>81/202</t>
+  </si>
+  <si>
+    <t>139/203</t>
+  </si>
+  <si>
+    <t>150/202</t>
+  </si>
+  <si>
+    <t>159/202</t>
+  </si>
+  <si>
+    <t>142/202</t>
+  </si>
+  <si>
+    <t>134/202</t>
+  </si>
+  <si>
+    <t>139/202</t>
+  </si>
+  <si>
+    <t>141/202</t>
+  </si>
+  <si>
+    <t>203/203</t>
+  </si>
+  <si>
+    <t>202/202</t>
+  </si>
+  <si>
+    <t>201/202</t>
   </si>
 </sst>
 </file>
@@ -528,34 +522,34 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>7.19</v>
+        <v>8.31</v>
       </c>
       <c r="D2">
-        <v>9.539999999999999</v>
+        <v>10.61</v>
       </c>
       <c r="E2">
-        <v>0.748</v>
+        <v>0.694</v>
       </c>
       <c r="F2">
-        <v>29997.9</v>
+        <v>26160.4</v>
       </c>
       <c r="G2">
-        <v>433807.9</v>
+        <v>483884.5</v>
       </c>
       <c r="H2">
-        <v>39.52</v>
+        <v>41.02</v>
       </c>
       <c r="I2" t="s">
         <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -566,31 +560,31 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>7.09</v>
+        <v>7.19</v>
       </c>
       <c r="D3">
-        <v>9.02</v>
+        <v>9.26</v>
       </c>
       <c r="E3">
-        <v>0.756</v>
+        <v>0.766</v>
       </c>
       <c r="F3">
-        <v>8302.9</v>
+        <v>2350.3</v>
       </c>
       <c r="G3">
-        <v>426761.2</v>
+        <v>423653.9</v>
       </c>
       <c r="H3">
-        <v>31.57</v>
+        <v>30.23</v>
       </c>
       <c r="I3" t="s">
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -598,22 +592,22 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="D4">
-        <v>9.609999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="E4">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="F4">
-        <v>79400.8</v>
+        <v>73356.39999999999</v>
       </c>
       <c r="G4">
-        <v>450801</v>
+        <v>458769</v>
       </c>
       <c r="H4">
         <v>42.56</v>
@@ -622,10 +616,10 @@
         <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -633,34 +627,34 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>8.119999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D5">
-        <v>10.33</v>
+        <v>10.31</v>
       </c>
       <c r="E5">
-        <v>0.6840000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="F5">
-        <v>113974.9</v>
+        <v>100536.8</v>
       </c>
       <c r="G5">
-        <v>472644.7</v>
+        <v>472759</v>
       </c>
       <c r="H5">
-        <v>32.44</v>
+        <v>32.09</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -668,34 +662,34 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>8.109999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D6">
-        <v>10.56</v>
+        <v>10.49</v>
       </c>
       <c r="E6">
-        <v>0.659</v>
+        <v>0.664</v>
       </c>
       <c r="F6">
-        <v>134800.5</v>
+        <v>76782.89999999999</v>
       </c>
       <c r="G6">
-        <v>486255.9</v>
+        <v>501947.4</v>
       </c>
       <c r="H6">
-        <v>36.01</v>
+        <v>32.06</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -706,31 +700,31 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>8.449999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="D7">
-        <v>10.57</v>
+        <v>10.65</v>
       </c>
       <c r="E7">
-        <v>0.651</v>
+        <v>0.668</v>
       </c>
       <c r="F7">
-        <v>90614.89999999999</v>
+        <v>135621.8</v>
       </c>
       <c r="G7">
-        <v>502619.6</v>
+        <v>485511.9</v>
       </c>
       <c r="H7">
-        <v>30.92</v>
+        <v>35.51</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -738,34 +732,34 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>8.529999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D8">
-        <v>11.72</v>
+        <v>12.1</v>
       </c>
       <c r="E8">
         <v>0.582</v>
       </c>
       <c r="F8">
-        <v>130733.2</v>
+        <v>123764.4</v>
       </c>
       <c r="G8">
-        <v>543600</v>
+        <v>552197.9</v>
       </c>
       <c r="H8">
-        <v>77.39</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -773,34 +767,34 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>7.97</v>
+        <v>8.01</v>
       </c>
       <c r="D9">
-        <v>10.65</v>
+        <v>10.73</v>
       </c>
       <c r="E9">
-        <v>0.66</v>
+        <v>0.665</v>
       </c>
       <c r="F9">
-        <v>134676.1</v>
+        <v>128343.9</v>
       </c>
       <c r="G9">
-        <v>485427.5</v>
+        <v>490335.4</v>
       </c>
       <c r="H9">
         <v>33.35</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
         <v>34</v>
-      </c>
-      <c r="K9" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/saidas/comparativo_preselecionados_valor.xlsx
+++ b/saidas/comparativo_preselecionados_valor.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>Modelo</t>
   </si>
@@ -58,70 +58,46 @@
     <t>ExtraTrees(EXT,j90)</t>
   </si>
   <si>
-    <t>POLY+ABR</t>
-  </si>
-  <si>
     <t>MAS+OHE+MAS+OHE+SE(SGDR)+MMS+LSVR</t>
   </si>
   <si>
     <t>VotingRegressor (RandomForest + ExtraTrees + XGBoost)</t>
   </si>
   <si>
-    <t>SE(ETR)+ABR</t>
-  </si>
-  <si>
-    <t>Voting(GBR+XGB+RFR)</t>
-  </si>
-  <si>
-    <t>72/203</t>
-  </si>
-  <si>
-    <t>86/202</t>
-  </si>
-  <si>
-    <t>89/202</t>
-  </si>
-  <si>
-    <t>72/202</t>
-  </si>
-  <si>
-    <t>69/202</t>
-  </si>
-  <si>
-    <t>73/202</t>
-  </si>
-  <si>
-    <t>81/202</t>
-  </si>
-  <si>
-    <t>139/203</t>
-  </si>
-  <si>
-    <t>150/202</t>
-  </si>
-  <si>
-    <t>159/202</t>
-  </si>
-  <si>
-    <t>142/202</t>
-  </si>
-  <si>
-    <t>134/202</t>
-  </si>
-  <si>
-    <t>139/202</t>
-  </si>
-  <si>
-    <t>141/202</t>
-  </si>
-  <si>
-    <t>203/203</t>
-  </si>
-  <si>
-    <t>202/202</t>
-  </si>
-  <si>
-    <t>201/202</t>
+    <t>94/260</t>
+  </si>
+  <si>
+    <t>112/259</t>
+  </si>
+  <si>
+    <t>107/259</t>
+  </si>
+  <si>
+    <t>84/259</t>
+  </si>
+  <si>
+    <t>104/259</t>
+  </si>
+  <si>
+    <t>168/260</t>
+  </si>
+  <si>
+    <t>193/259</t>
+  </si>
+  <si>
+    <t>199/259</t>
+  </si>
+  <si>
+    <t>169/259</t>
+  </si>
+  <si>
+    <t>181/259</t>
+  </si>
+  <si>
+    <t>260/260</t>
+  </si>
+  <si>
+    <t>259/259</t>
   </si>
 </sst>
 </file>
@@ -479,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -522,34 +498,34 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>8.31</v>
+        <v>8.48</v>
       </c>
       <c r="D2">
-        <v>10.61</v>
+        <v>10.75</v>
       </c>
       <c r="E2">
-        <v>0.694</v>
+        <v>0.696</v>
       </c>
       <c r="F2">
-        <v>26160.4</v>
+        <v>46273.5</v>
       </c>
       <c r="G2">
-        <v>483884.5</v>
+        <v>486650.6</v>
       </c>
       <c r="H2">
         <v>41.02</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
         <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -560,31 +536,31 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>7.19</v>
+        <v>7.31</v>
       </c>
       <c r="D3">
-        <v>9.26</v>
+        <v>9.56</v>
       </c>
       <c r="E3">
-        <v>0.766</v>
+        <v>0.753</v>
       </c>
       <c r="F3">
-        <v>2350.3</v>
+        <v>31445.1</v>
       </c>
       <c r="G3">
-        <v>423653.9</v>
+        <v>439670.9</v>
       </c>
       <c r="H3">
-        <v>30.23</v>
+        <v>39.85</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
         <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -595,31 +571,31 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>7.3</v>
+        <v>7.47</v>
       </c>
       <c r="D4">
-        <v>9.84</v>
+        <v>9.94</v>
       </c>
       <c r="E4">
         <v>0.718</v>
       </c>
       <c r="F4">
-        <v>73356.39999999999</v>
+        <v>94314.60000000001</v>
       </c>
       <c r="G4">
-        <v>458769</v>
+        <v>461355.3</v>
       </c>
       <c r="H4">
         <v>42.56</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -630,31 +606,31 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>8.140000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="D5">
-        <v>10.31</v>
+        <v>10.58</v>
       </c>
       <c r="E5">
-        <v>0.695</v>
+        <v>0.672</v>
       </c>
       <c r="F5">
-        <v>100536.8</v>
+        <v>78391.2</v>
       </c>
       <c r="G5">
-        <v>472759</v>
+        <v>502068.5</v>
       </c>
       <c r="H5">
-        <v>32.09</v>
+        <v>32.06</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -662,139 +638,34 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>8.390000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="D6">
-        <v>10.49</v>
+        <v>10.77</v>
       </c>
       <c r="E6">
-        <v>0.664</v>
+        <v>0.673</v>
       </c>
       <c r="F6">
-        <v>76782.89999999999</v>
+        <v>147360.4</v>
       </c>
       <c r="G6">
-        <v>501947.4</v>
+        <v>485195.7</v>
       </c>
       <c r="H6">
-        <v>32.06</v>
+        <v>35.51</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="D7">
-        <v>10.65</v>
-      </c>
-      <c r="E7">
-        <v>0.668</v>
-      </c>
-      <c r="F7">
-        <v>135621.8</v>
-      </c>
-      <c r="G7">
-        <v>485511.9</v>
-      </c>
-      <c r="H7">
-        <v>35.51</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="D8">
-        <v>12.1</v>
-      </c>
-      <c r="E8">
-        <v>0.582</v>
-      </c>
-      <c r="F8">
-        <v>123764.4</v>
-      </c>
-      <c r="G8">
-        <v>552197.9</v>
-      </c>
-      <c r="H8">
-        <v>79.31999999999999</v>
-      </c>
-      <c r="I8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>8.01</v>
-      </c>
-      <c r="D9">
-        <v>10.73</v>
-      </c>
-      <c r="E9">
-        <v>0.665</v>
-      </c>
-      <c r="F9">
-        <v>128343.9</v>
-      </c>
-      <c r="G9">
-        <v>490335.4</v>
-      </c>
-      <c r="H9">
-        <v>33.35</v>
-      </c>
-      <c r="I9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
